--- a/AAII_Financials/Quarterly/CVS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CVS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>CVS</t>
   </si>
@@ -656,519 +656,531 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="36" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="37" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>105455000</v>
+      </c>
+      <c r="E8" s="3">
         <v>99852000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>105099000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>102239000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>98428000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>94068000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>96955000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>94878000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>90840000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>87983000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>93545000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>89487000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>88647000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>84944000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>83846000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>81159000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>80636000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>76826000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>76604000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>73794000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>72616000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>69097000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>69554000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>67056000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>65341000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>66755000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>66889000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>64810000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>63431000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>61646000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>54909000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>47490000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>46922000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>45743000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>48406000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>46181000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>45685000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>44514000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>45971000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>44615000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>90347000</v>
+      </c>
+      <c r="E9" s="3">
         <v>84802000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>92126000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>89065000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>85322000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>80192000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>84811000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>82870000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>77851000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>75876000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>79937000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>76187000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>75318000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>71903000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>69987000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>67766000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>66780000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>63432000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>46378000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>45011000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>43520000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>40894000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>42452000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>40940000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>40242000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>40347000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>42065000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>40437000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>38970000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>37247000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>38165000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>39502000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>38876000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>76339000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>37682000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>39064000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>77509000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>37934000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>38365000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>37123000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>15108000</v>
+      </c>
+      <c r="E10" s="3">
         <v>15050000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12973000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>13174000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13106000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13876000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12144000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12008000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12989000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12107000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13608000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13300000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>13329000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>13041000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>13859000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>13393000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>13856000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13394000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>30226000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>28783000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>29096000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>28203000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>27102000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>26116000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>25099000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>26408000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24824000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24373000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>24461000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>24399000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>16744000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>7988000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>8046000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-30596000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>10724000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>7117000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>-31824000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>6580000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>7606000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>7492000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1211,8 +1223,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1333,8 +1346,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1455,175 +1471,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E14" s="3">
         <v>12000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>17000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5672000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>865000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>438000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-428000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1227000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>102000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>160000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>239000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>105000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>664000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>392000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>99000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>5220000</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>484000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1478000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>814000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>40000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>41000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>812000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>552000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>70000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>69000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>260000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>124000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>67000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>108000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>2228000</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>3921000</v>
       </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>46000</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="3">
         <v>135000</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
       <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3">
         <v>101000</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1126000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1115000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1147000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1134000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1171000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1154000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1147000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1161000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1151000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1138000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1134000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>1127000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1104000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1001000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1699,8 +1721,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1740,252 +1765,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>101383000</v>
+      </c>
+      <c r="E17" s="3">
         <v>95734000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>103447000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>99923000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>95669000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>90776000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>95175000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>93369000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>88087000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>86006000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>90107000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>85969000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>85023000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>81440000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>80187000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>85078000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>75967000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>73281000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>74464000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>71096000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>68290000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>65520000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>67704000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>64573000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>60661000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>63297000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>63852000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>61961000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>60099000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>58956000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>53600000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>44916000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>48295000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>43747000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>45277000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>43682000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>43568000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>42721000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>42976000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>41892000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4072000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4118000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1652000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2316000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2759000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3292000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1780000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1509000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2753000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1977000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3438000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3518000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3624000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3504000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3659000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-3919000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4669000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3545000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2140000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2698000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4326000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3577000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>1850000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2483000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4680000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>3458000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>3037000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2849000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>3332000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2690000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1309000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2574000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-1373000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1996000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>3129000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2499000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2117000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1793000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2995000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2723000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2028,43 +2060,44 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-32000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>88000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-26000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-29000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-28000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>79000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-25000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-25000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>72000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-22000</v>
       </c>
       <c r="O20" s="3">
         <v>-22000</v>
@@ -2073,43 +2106,43 @@
         <v>-22000</v>
       </c>
       <c r="Q20" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="R20" s="3">
         <v>595000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>41000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>43000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>42000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>38000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>49000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>45000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>50000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>53000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>54000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>45000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>54000</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>31000</v>
       </c>
       <c r="AD20" s="3">
         <v>31000</v>
@@ -2121,525 +2154,540 @@
         <v>31000</v>
       </c>
       <c r="AG20" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-474000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>-3000</v>
       </c>
       <c r="AJ20" s="3">
         <v>-3000</v>
       </c>
       <c r="AK20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-17000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-187000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>6000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-2000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5229000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5265000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2711000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3476000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3959000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>4474000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2848000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2695000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>3928000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3140000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4500000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4667000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4750000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4527000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5303000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-2822000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5799000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4642000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3293000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3881000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5508000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4753000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>3042000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>3651000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5827000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4598000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4164000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3972000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4435000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3832000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1642000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3193000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-729000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>2637000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>3734000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2927000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2737000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>2411000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>3629000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>3332000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>757000</v>
+      </c>
+      <c r="E22" s="3">
         <v>774000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>787000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>784000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>763000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>785000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>758000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>752000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>732000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>716000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>690000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>693000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>686000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>589000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1104000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>566000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>583000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>586000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>608000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>602000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>636000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>657000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>678000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>731000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>765000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>733000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>734000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>747000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>772000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>782000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>733000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>674000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>689000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>523000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>303000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>250000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>251000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>258000</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>248000</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>258000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3977000</v>
+      </c>
+      <c r="E23" s="3">
         <v>3938000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1354000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3482000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1647000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2617000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2126000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>105000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2337000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1580000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2705000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3019000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2570000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2879000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3150000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4444000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4129000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3001000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1570000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2145000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3735000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>2970000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1225000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1806000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3960000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2779000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2334000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2133000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2591000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1939000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>102000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1899000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-2065000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1470000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2809000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2062000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1863000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1534000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2753000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2463000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>982000</v>
+      </c>
+      <c r="E24" s="3">
         <v>981000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1569000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>508000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>634000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>835000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>503000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>34000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>569000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>456000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>658000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>754000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>656000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>737000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>818000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1045000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1090000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>646000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>274000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>558000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>944000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>746000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>241000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>587000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>974000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>767000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>590000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>604000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>660000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>512000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>624000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>509000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>497000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>472000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1022000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>777000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>766000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>572000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1046000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>921000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2760,252 +2808,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2995000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2957000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2923000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3990000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1013000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1782000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1623000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>71000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1768000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1124000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2047000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2265000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1914000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2142000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2332000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3399000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3039000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2355000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1296000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1587000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>2791000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2224000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>984000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1219000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>2986000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>2012000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1744000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1529000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1931000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1427000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-522000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1390000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-2562000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>998000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1787000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1285000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1097000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>962000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1707000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1542000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2943000</v>
+        <v>2979000</v>
       </c>
       <c r="E27" s="3">
         <v>2943000</v>
       </c>
       <c r="F27" s="3">
+        <v>2943000</v>
+      </c>
+      <c r="G27" s="3">
         <v>-3975000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1021000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1779000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1644000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>87000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1770000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1113000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2046000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2261000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1901000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2136000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2334000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3406000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3029000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2354000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1306000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1598000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2783000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2223000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>982000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>1224000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>2975000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>2007000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1750000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1530000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1935000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1419000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-521000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1389000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-2562000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>996000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1775000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1282000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1093000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>966000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1698000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1535000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3126,8 +3183,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3176,17 +3236,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -3194,11 +3254,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-9000</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3206,8 +3266,8 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3215,41 +3275,44 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>101000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>1500000</v>
       </c>
-      <c r="AL29" s="3">
-        <v>0</v>
-      </c>
       <c r="AM29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="3">
         <v>1000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-9000</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
       <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3370,8 +3433,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3492,43 +3558,46 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E32" s="3">
         <v>32000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-88000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>26000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>29000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>28000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-79000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>25000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>25000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-72000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>22000</v>
       </c>
       <c r="O32" s="3">
         <v>22000</v>
@@ -3537,43 +3606,43 @@
         <v>22000</v>
       </c>
       <c r="Q32" s="3">
+        <v>22000</v>
+      </c>
+      <c r="R32" s="3">
         <v>-595000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-41000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-43000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-42000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-38000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-49000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-45000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-50000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-54000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-45000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-54000</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>-31000</v>
       </c>
       <c r="AD32" s="3">
         <v>-31000</v>
@@ -3585,159 +3654,165 @@
         <v>-31000</v>
       </c>
       <c r="AG32" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="AH32" s="3">
         <v>474000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1000</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>3000</v>
       </c>
       <c r="AJ32" s="3">
         <v>3000</v>
       </c>
       <c r="AK32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AL32" s="3">
         <v>17000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>187000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>3000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2943000</v>
+        <v>2979000</v>
       </c>
       <c r="E33" s="3">
         <v>2943000</v>
       </c>
       <c r="F33" s="3">
+        <v>2943000</v>
+      </c>
+      <c r="G33" s="3">
         <v>-3975000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1021000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1779000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1644000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>87000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1770000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1113000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2046000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2261000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1901000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2136000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2334000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3406000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3029000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2354000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1306000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1598000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2783000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2223000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>973000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>1224000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>2975000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>2007000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1750000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1530000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1935000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1419000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-420000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1389000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-2563000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>996000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3275000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1282000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1094000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>957000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1698000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3858,257 +3933,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2943000</v>
+        <v>2979000</v>
       </c>
       <c r="E35" s="3">
         <v>2943000</v>
       </c>
       <c r="F35" s="3">
+        <v>2943000</v>
+      </c>
+      <c r="G35" s="3">
         <v>-3975000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1021000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1779000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1644000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>87000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1770000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1113000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2046000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2261000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1901000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2136000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2334000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3406000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3029000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2354000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1306000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1598000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2783000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2223000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>973000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>1224000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>2975000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>2007000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1750000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1530000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1935000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1419000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-420000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1389000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-2563000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>996000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3275000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1282000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1094000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>957000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1698000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4151,8 +4235,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4195,835 +4280,854 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11329000</v>
+      </c>
+      <c r="E41" s="3">
         <v>9542000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8453000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9098000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11787000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>10076000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8586000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6875000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12507000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9801000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8196000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13043000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13807000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14618000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12945000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17197000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12116000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8442000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>9408000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9826000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7119000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5598000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7854000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9256000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>14869000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10081000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5683000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5193000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6063000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5896000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4059000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>41587000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>43815000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>42023000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1696000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2485000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2094000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2217000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3371000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2189000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2629000</v>
+      </c>
+      <c r="E42" s="3">
         <v>2260000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2145000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2134000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2386000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2578000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2407000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2805000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3755000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>3288000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3259000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3145000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3080000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3102000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2778000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>2792000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2877000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2900000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3117000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3015000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3006000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3190000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3000000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2831000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2596000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2632000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2373000</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2334000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2462000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2426000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>2522000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>105000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>119000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>111000</v>
-      </c>
-      <c r="AL42" s="3">
-        <v>75000</v>
       </c>
       <c r="AM42" s="3">
         <v>75000</v>
       </c>
       <c r="AN42" s="3">
+        <v>75000</v>
+      </c>
+      <c r="AO42" s="3">
         <v>85000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>87000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>74000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40309000</v>
+      </c>
+      <c r="E43" s="3">
         <v>40992000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>39779000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>43857000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40651000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>39625000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>36469000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>36179000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>32385000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>32217000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>35227000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>32927000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>29546000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28331000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>27276000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>26317000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>27233000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>26451000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24431000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>25283000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>24164000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>23855000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>21742000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>23816000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>22520000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23037000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>19617000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>19789000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>18174000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>19509000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>17631000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>14837000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>14158000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>13964000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>13181000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>12440000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>12274000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>12114000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>12164000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>13625000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17622000</v>
+      </c>
+      <c r="E44" s="3">
         <v>17770000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>19246000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>18962000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17447000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17385000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>18107000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17649000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16068000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16346000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>18025000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17954000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>17291000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>18263000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>19090000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>18058000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>17375000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>18160000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>17760000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>17399000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>16979000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>17618000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>18496000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>17478000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>16519000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>16976000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>17516000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>16028000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>15511000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>15448000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>16450000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>14818000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>14922000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>14824000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>15296000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>14147000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>14271000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>14306000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>14760000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>14348000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3457000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4239000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5032000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3001000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3335000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3462000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2981000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3770000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5183000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5770000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3061000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2978000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3945000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4285000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3544000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3977000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2541000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5530000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5292000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5319000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5291000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5458000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5277000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5830000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6002000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6232000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5113000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4841000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4691000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4578000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4581000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>634000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>799000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>868000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>945000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>776000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>690000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>735000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>660000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>703000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>75346000</v>
+      </c>
+      <c r="E46" s="3">
         <v>74817000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>74714000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>77109000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>75649000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>73191000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>68645000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>67343000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>69952000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>67473000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>67858000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>70143000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>67756000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>68706000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>65633000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>68341000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>62142000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>61483000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>60008000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>60842000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>56559000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>55719000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>56369000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>59211000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>62506000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>58958000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>50302000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>48185000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>46901000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>47857000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>45243000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>71981000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>73790000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>71798000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>31229000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>29923000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>29404000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>29457000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>31042000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>30939000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>33247000</v>
+      </c>
+      <c r="E47" s="3">
         <v>32407000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>32669000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>31553000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>29858000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>28906000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>28934000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>28939000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>25028000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>24074000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>23019000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>21667000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>22114000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>21612000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>21096000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>20565000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>21124000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>22595000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>23025000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>22370000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>22136000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>21025000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>20812000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>20216000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>18594000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>16840000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>17314000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>17342000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>16973000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>16410000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>15732000</v>
-      </c>
-      <c r="AH47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI47" s="3" t="s">
         <v>8</v>
@@ -5040,8 +5144,8 @@
       <c r="AM47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AN47" s="3">
-        <v>0</v>
+      <c r="AN47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AO47" s="3">
         <v>0</v>
@@ -5049,252 +5153,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27619000</v>
+      </c>
+      <c r="E48" s="3">
         <v>27778000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28056000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28109000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28337000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28560000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28937000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28959000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29933000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30082000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>30435000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>30586000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>30704000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30532000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30745000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>30896000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>31326000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>31645000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>32018000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33233000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33140000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33153000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>33335000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>32833000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>32792000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>32818000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>32904000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>32408000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32348000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>32340000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11349000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>10419000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>10249000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>10144000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>10292000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>9914000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>10073000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>10057000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>10175000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>9901000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>110122000</v>
+      </c>
+      <c r="E49" s="3">
         <v>110548000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>110986000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>111462000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>117427000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>117773000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>118595000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>119089000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>119583000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>120042000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>120506000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>120885000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>121378000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>110425000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>102953000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>103243000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>106695000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>107603000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>108147000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>108666000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>109632000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>110191000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>110694000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>111276000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>112282000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>112720000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>112870000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>113203000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>113648000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>114222000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>115202000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>47382000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>47542000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>51503000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>52081000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>51472000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>51484000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>51653000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>51760000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>51781000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5415,8 +5528,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5537,130 +5653,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7434000</v>
+      </c>
+      <c r="E52" s="3">
         <v>7424000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7113000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7094000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7072000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7155000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>8104000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8097000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7985000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8072000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7910000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8025000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8119000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8055000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7604000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8167000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8992000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>9547000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9801000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9780000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9697000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9518000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9505000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9362000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9321000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9303000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9059000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8975000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9034000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>8939000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>8930000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1724000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1709000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1694000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1529000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1544000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1564000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1503000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1485000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1535000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5781,130 +5903,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>253768000</v>
+      </c>
+      <c r="E54" s="3">
         <v>252974000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>253538000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>255327000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>258343000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>255585000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>253215000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>252427000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>252481000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>249743000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>249728000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>251306000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>250071000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>239330000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>228275000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>231212000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>230279000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>232873000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>232999000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>234891000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>231164000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>229606000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>230715000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>232898000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>235495000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>230639000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>222449000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>220113000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>218904000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>219768000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>196456000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>131506000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>133290000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>135139000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>95131000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>92853000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>92525000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>92670000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>94462000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>94156000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5947,8 +6075,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5991,740 +6120,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17167000</v>
+      </c>
+      <c r="E57" s="3">
         <v>16922000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17641000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17764000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17258000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16534000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15892000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15713000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14416000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13717000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14897000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14874000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13367000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12527000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>44403000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>43437000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>42031000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>41570000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>38682000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>39468000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>36691000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>35358000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>34869000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>34992000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>32822000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>33257000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>30972000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>29555000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>27986000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>26818000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>26437000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>21161000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>20313000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>18982000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>8863000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>7899000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>7874000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>7344000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>7946000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>7584000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3872000</v>
+      </c>
+      <c r="E58" s="3">
         <v>4484000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5805000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7237000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11106000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7579000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7494000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7622000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5642000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8356000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4713000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3873000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4108000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3457000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1778000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1363000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4019000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4217000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4205000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1561000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>60000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2674000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5440000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5443000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>8192000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>6083000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3781000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4848000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4340000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6898000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1985000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2139000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3540000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3542000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>4821000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>2403000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1142000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1811000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1916000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1123000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>27212000</v>
+      </c>
+      <c r="E59" s="3">
         <v>27224000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27522000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28239000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27487000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27432000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25493000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26055000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>26408000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24645000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24164000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27852000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27063000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>26796000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>23240000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27609000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>22407000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>23993000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>24920000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>23680000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>22560000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>22072000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>21708000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21609000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>22680000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>20220000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>18550000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>18141000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17050000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16915000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>15587000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6160000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>7640000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>7724000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>16964000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>18211000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>17841000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>18133000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>16388000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>18034000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>87041000</v>
+      </c>
+      <c r="E60" s="3">
         <v>86406000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>88692000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>92695000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>94162000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>88961000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>84609000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>84627000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>81386000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>83319000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>79189000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>81553000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>79206000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>75054000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>69421000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>72409000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>68457000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>69780000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>67807000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>64709000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>59311000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>60104000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>62017000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>62044000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>63694000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>59560000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>53303000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>52544000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>49376000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>50631000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>44009000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>29460000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>31493000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>30248000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30648000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>28513000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>26857000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>27288000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>26250000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>26741000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>72434000</v>
+      </c>
+      <c r="E61" s="3">
         <v>73861000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>74145000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>74515000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>71618000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>73634000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>75426000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>75082000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>78180000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>73436000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>74672000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>76223000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>78028000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>73021000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>50476000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>50848000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>50797000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>52063000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>51971000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>56832000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>59294000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>59270000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>59207000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>61552000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>63481000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>65735000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>64699000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>64206000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>66941000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>67888000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>71444000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>60747000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>61569000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>61552000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>22181000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>23386000</v>
-      </c>
-      <c r="AM61" s="3">
-        <v>25622000</v>
       </c>
       <c r="AN61" s="3">
         <v>25622000</v>
       </c>
       <c r="AO61" s="3">
+        <v>25622000</v>
+      </c>
+      <c r="AP61" s="3">
         <v>25615000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>25610000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10628000</v>
+      </c>
+      <c r="E62" s="3">
         <v>11299000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>11322000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11460000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11409000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12216000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13475000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>13980000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13752000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>14654000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>14731000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>14770000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15247000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15580000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>36609000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>36944000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>35519000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>36890000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37840000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>38732000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>38994000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>39068000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>39790000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>40190000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>39965000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>39870000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>40277000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>40430000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>40988000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>41243000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>22460000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>4677000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>4617000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>4662000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>4607000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>6086000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5899000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5918000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5763000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>5851000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6845,8 +6993,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6967,8 +7118,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7089,130 +7243,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>173869000</v>
+      </c>
+      <c r="E66" s="3">
         <v>175337000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>178156000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>182217000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>180792000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>178475000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>177485000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>177321000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>177370000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>175593000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>173092000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>176796000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>177069000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>167750000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>156806000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>160529000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>155095000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>159043000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>157924000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>160583000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>157920000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>158756000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>161326000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>164091000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>167473000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>165499000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>158585000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>157499000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>157622000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>160082000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>138231000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>94888000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>97683000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>96466000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>57440000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>57990000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>58383000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>58833000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>57632000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>58207000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7255,8 +7415,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7377,8 +7538,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7499,8 +7663,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7621,8 +7788,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7743,130 +7913,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>65398000</v>
+      </c>
+      <c r="E72" s="3">
         <v>63282000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>61196000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>59107000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>63936000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>63768000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>62837000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>62038000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>62797000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>61873000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>61604000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>60343000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>58868000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>57753000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>56398000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>54571000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>58710000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>56488000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>54906000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>54264000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>53331000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>51203000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>49640000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>49328000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>48768000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>46455000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>45108000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>44017000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>43136000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>41859000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>40911000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>41843000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>40965000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>44040000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>43556000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>40779000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>40005000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>39419000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>38983000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>37732000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7987,8 +8163,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8109,8 +8288,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8231,130 +8413,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>79702000</v>
+      </c>
+      <c r="E76" s="3">
         <v>77456000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>75214000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>72928000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>77379000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>76929000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>75560000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>74944000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>74930000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>73968000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>76461000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>74337000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>72726000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>71382000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>71469000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>70683000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75184000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>73830000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>75075000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>74308000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>73244000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>70850000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>69389000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>68807000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>68022000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>65140000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>63864000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>62614000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>61282000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>59686000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>58225000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>36618000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>35607000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>38673000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>37691000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>34863000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>34142000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>33837000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>36830000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>35949000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8475,257 +8663,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2943000</v>
+        <v>2979000</v>
       </c>
       <c r="E81" s="3">
         <v>2943000</v>
       </c>
       <c r="F81" s="3">
+        <v>2943000</v>
+      </c>
+      <c r="G81" s="3">
         <v>-3975000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1021000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1779000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1644000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>87000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1770000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1113000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2046000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2261000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1901000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2136000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2334000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3406000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3029000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2354000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1306000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1598000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2783000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2223000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>973000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>1224000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>2975000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>2007000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1750000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1530000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1935000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1419000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-420000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1389000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-2563000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>996000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3275000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1282000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1094000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>957000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1698000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1534000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8768,130 +8965,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>677000</v>
+      </c>
+      <c r="E83" s="3">
         <v>655000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>644000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>654000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>644000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>630000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>625000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>618000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>619000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>599000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>638000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>592000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>622000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>587000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1049000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1056000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1087000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1055000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1115000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1134000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1137000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>1126000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1139000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1114000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>1102000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>1086000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1096000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>1092000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>1072000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>1111000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>807000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>620000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>647000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>644000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>622000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>615000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>623000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>619000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>628000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>611000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9012,8 +9213,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9134,8 +9338,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9256,8 +9463,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9378,8 +9588,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9500,130 +9713,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6345000</v>
+      </c>
+      <c r="E89" s="3">
         <v>4249000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3390000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>796000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1897000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4556000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1860000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-745000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3089000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4903000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2636000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2716000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5908000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7438000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1952000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>9123000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5443000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3563000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4005000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5521000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5847000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>2892000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>3567000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1874000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>7119000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3305000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2634000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2928000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>5338000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1948000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2479000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1097000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2934000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2355000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-136000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>2611000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>1999000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>3533000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2121000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>3934000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9666,130 +9885,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-691000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-849000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-784000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-698000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-607000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-743000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-768000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-670000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-638000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-705000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-911000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-545000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-591000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-984000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-688000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-580000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-408000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1051000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-597000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-608000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-486000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-829000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-713000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-534000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-448000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-742000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-567000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-601000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-573000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-716000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-585000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-540000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-430000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-482000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-506000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-524000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-431000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-914000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1234000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-1010000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9910,8 +10133,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10032,130 +10258,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1884000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-874000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1998000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2087000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1024000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-762000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-547000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3347000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1625000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2094000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1242000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-771000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10362000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8514000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-119000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-805000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2130000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1993000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1440000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-847000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1107000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1867000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1234000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1370000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1333000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1597000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-709000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-829000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-910000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-891000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-41899000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-634000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-621000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-131000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1310000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-433000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-597000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-537000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-818000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-421000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10198,100 +10430,101 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>878000</v>
+      </c>
+      <c r="E96" s="3">
         <v>847000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>845000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>846000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>866000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>840000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>838000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>837000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>858000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>840000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>779000</v>
       </c>
       <c r="N96" s="3">
         <v>779000</v>
       </c>
       <c r="O96" s="3">
+        <v>779000</v>
+      </c>
+      <c r="P96" s="3">
         <v>795000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>779000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-719000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-726000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-740000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-722000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-660000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-659000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-650000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-656000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-644000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-665000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-663000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-652000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-651000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-646000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-657000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-649000</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-510000</v>
       </c>
       <c r="AH96" s="3">
         <v>-510000</v>
@@ -10300,28 +10533,31 @@
         <v>-510000</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-510000</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-508000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-510000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-511000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-512000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-516000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-456000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-455000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10442,8 +10678,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10564,8 +10803,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10686,130 +10928,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2693000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2318000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2032000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1382000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>806000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2332000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>431000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1588000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1249000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1227000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-972000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2697000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3626000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2726000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2187000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-3218000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2461000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2650000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-2914000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1884000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-3373000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-3185000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-3276000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6117000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-978000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2675000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1440000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2968000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4258000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>816000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1892000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-2693000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-520000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>38140000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>670000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1786000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1502000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-4133000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-121000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-2442000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10852,8 +11100,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10897,15 +11145,15 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-      <c r="AF101" s="3" t="s">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
         <v>0</v>
       </c>
@@ -10913,11 +11161,11 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>1000</v>
       </c>
-      <c r="AL101" s="3">
-        <v>0</v>
-      </c>
       <c r="AM101" s="3">
         <v>0</v>
       </c>
@@ -10930,126 +11178,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1768000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1057000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-640000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2673000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1679000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1462000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1744000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5680000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2713000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1582000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4850000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-752000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-828000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1650000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4258000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5100000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>852000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1080000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-349000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2790000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1367000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2160000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-943000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-5613000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>4808000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>4383000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>485000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-869000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>170000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1873000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-37532000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2230000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1793000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>40364000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-775000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>392000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-100000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1182000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>1062000</v>
       </c>
     </row>
